--- a/artfynd/A 2576-2024 artfynd.xlsx
+++ b/artfynd/A 2576-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2576-2024 artfynd.xlsx
+++ b/artfynd/A 2576-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71838227</v>
+        <v>72026926</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,52 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bredhälla, Bredhälla, Sm</t>
+          <t>Bredhälla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522673.6972269448</v>
+        <v>522835</v>
       </c>
       <c r="R2" t="n">
-        <v>6325950.832082964</v>
+        <v>6325869</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -802,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71838170</v>
+        <v>71838398</v>
       </c>
       <c r="B3" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,52 +795,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredhälla, Bredhälla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522680.6546824942</v>
+        <v>522678</v>
       </c>
       <c r="R3" t="n">
-        <v>6325973.15440751</v>
+        <v>6325846</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,19 +859,14 @@
           <t>2018-06-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>torraka av tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72026926</v>
+        <v>72810723</v>
       </c>
       <c r="B4" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,48 +904,57 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bredhälla, Sm</t>
+          <t>Bredhälla, Bredhälla, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522834.8054298341</v>
+        <v>522688</v>
       </c>
       <c r="R4" t="n">
-        <v>6325869.102350679</v>
+        <v>6325885</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,22 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +992,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1053,32 +1010,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72810723</v>
+        <v>71837867</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,20 +1055,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredhälla, Bredhälla, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522687.6723963607</v>
+        <v>522599</v>
       </c>
       <c r="R5" t="n">
-        <v>6325885.142430726</v>
+        <v>6325930</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1143,22 +1094,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,37 +1126,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>71838331</v>
+        <v>71838170</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1225,12 +1161,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>vilstadium</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1240,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522797.7370375714</v>
+        <v>522681</v>
       </c>
       <c r="R6" t="n">
-        <v>6325875.42031342</v>
+        <v>6325973</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,19 +1209,9 @@
           <t>2018-06-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1312,65 +1238,63 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72810599</v>
+        <v>71838227</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredhälla, Sm</t>
+          <t>Bredhälla, Bredhälla, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522732.1737495159</v>
+        <v>522674</v>
       </c>
       <c r="R7" t="n">
-        <v>6325913.649968484</v>
+        <v>6325951</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1394,22 +1318,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,7 +1332,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1437,15 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>72810180</v>
+        <v>71838331</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1380,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1480,22 +1388,25 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredhälla, Sm</t>
+          <t>Bredhälla, Bredhälla, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522705.3737282859</v>
+        <v>522798</v>
       </c>
       <c r="R8" t="n">
-        <v>6325835.234728674</v>
+        <v>6325875</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1519,22 +1430,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,7 +1444,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1562,15 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>72810690</v>
+        <v>72026852</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,15 +1492,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1614,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>522720.0226920572</v>
+        <v>522814</v>
       </c>
       <c r="R9" t="n">
-        <v>6325944.563951829</v>
+        <v>6325860</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1644,22 +1543,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,15 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72810335</v>
+        <v>72026887</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,15 +1606,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1739,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522747.1943497184</v>
+        <v>522803</v>
       </c>
       <c r="R10" t="n">
-        <v>6325856.118630601</v>
+        <v>6325884</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1769,22 +1657,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1812,15 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>72026852</v>
+        <v>72126121</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,17 +1720,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1868,13 +1741,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522814.1617602356</v>
+        <v>522851</v>
       </c>
       <c r="R11" t="n">
-        <v>6325859.748476798</v>
+        <v>6325851</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,22 +1771,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>enstaka i knopp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1941,15 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>72026887</v>
+        <v>72810180</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1976,19 +1839,15 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1997,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522802.5934601809</v>
+        <v>522705</v>
       </c>
       <c r="R12" t="n">
-        <v>6325883.599991152</v>
+        <v>6325835</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2027,22 +1886,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2070,15 +1919,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>72810229</v>
+        <v>72810208</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2105,7 +1949,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2122,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>522710.1916035239</v>
+        <v>522702</v>
       </c>
       <c r="R13" t="n">
-        <v>6325850.480079533</v>
+        <v>6325850</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2155,19 +1999,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2195,15 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>72810589</v>
+        <v>72810229</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2230,7 +2059,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2247,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>522730.5459532673</v>
+        <v>522710</v>
       </c>
       <c r="R14" t="n">
-        <v>6325912.553979632</v>
+        <v>6325850</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2280,19 +2109,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2320,15 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>72810558</v>
+        <v>72810252</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2169,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2372,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522718.7082198702</v>
+        <v>522724</v>
       </c>
       <c r="R15" t="n">
-        <v>6325886.399760175</v>
+        <v>6325851</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2405,19 +2219,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2448,12 +2252,7 @@
         <v>72810270</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522723.2231420837</v>
+        <v>522723</v>
       </c>
       <c r="R16" t="n">
-        <v>6325857.617522856</v>
+        <v>6325858</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2530,19 +2329,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2570,15 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>72810665</v>
+        <v>72810312</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2389,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2622,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522710.3126305055</v>
+        <v>522741</v>
       </c>
       <c r="R17" t="n">
-        <v>6325927.661516277</v>
+        <v>6325860</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2655,19 +2439,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2695,15 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>72810513</v>
+        <v>72810335</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2499,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2747,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>522754.711110184</v>
+        <v>522747</v>
       </c>
       <c r="R18" t="n">
-        <v>6325875.727025143</v>
+        <v>6325856</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2780,19 +2549,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2820,15 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>72810252</v>
+        <v>72810392</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2855,7 +2609,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2872,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>522723.8065386364</v>
+        <v>522678</v>
       </c>
       <c r="R19" t="n">
-        <v>6325850.554821275</v>
+        <v>6325872</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2905,19 +2659,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2945,15 +2689,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>72810499</v>
+        <v>72810470</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2980,7 +2719,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2997,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>522724.7972362795</v>
+        <v>522688</v>
       </c>
       <c r="R20" t="n">
-        <v>6325868.496766726</v>
+        <v>6325868</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3030,19 +2769,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3070,15 +2799,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>72810528</v>
+        <v>72810481</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3122,10 +2846,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522740.4471246367</v>
+        <v>522706</v>
       </c>
       <c r="R21" t="n">
-        <v>6325894.672063828</v>
+        <v>6325868</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3155,19 +2879,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3195,15 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>72810481</v>
+        <v>72810494</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3230,7 +2939,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3247,10 +2956,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522705.736409716</v>
+        <v>522714</v>
       </c>
       <c r="R22" t="n">
-        <v>6325868.392136076</v>
+        <v>6325867</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3280,19 +2989,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3320,15 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>72810208</v>
+        <v>72810499</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3355,7 +3049,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3372,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522702.022642388</v>
+        <v>522725</v>
       </c>
       <c r="R23" t="n">
-        <v>6325850.435255989</v>
+        <v>6325868</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3405,19 +3099,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3445,15 +3129,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>72810392</v>
+        <v>72810513</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3480,7 +3159,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3497,10 +3176,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522677.941211693</v>
+        <v>522755</v>
       </c>
       <c r="R24" t="n">
-        <v>6325872.044420094</v>
+        <v>6325876</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3530,19 +3209,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,15 +3239,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>72810571</v>
+        <v>72810528</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3605,7 +3269,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3622,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522711.5628882712</v>
+        <v>522740</v>
       </c>
       <c r="R25" t="n">
-        <v>6325898.318112389</v>
+        <v>6325895</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3655,19 +3319,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3695,15 +3349,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>72810628</v>
+        <v>72810543</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3730,7 +3379,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3747,10 +3396,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522744.0949634161</v>
+        <v>522732</v>
       </c>
       <c r="R26" t="n">
-        <v>6325924.585928356</v>
+        <v>6325892</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3780,19 +3429,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3820,15 +3459,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>72810312</v>
+        <v>72810558</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3855,7 +3489,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3872,10 +3506,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522741.1828779</v>
+        <v>522719</v>
       </c>
       <c r="R27" t="n">
-        <v>6325859.890304745</v>
+        <v>6325886</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3905,19 +3539,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3945,15 +3569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>72810681</v>
+        <v>72810571</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3980,7 +3599,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3997,10 +3616,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522703.1972129215</v>
+        <v>522712</v>
       </c>
       <c r="R28" t="n">
-        <v>6325934.144724458</v>
+        <v>6325898</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4030,19 +3649,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4070,15 +3679,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>72810609</v>
+        <v>72810589</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4105,7 +3709,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4122,10 +3726,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522711.4584823753</v>
+        <v>522731</v>
       </c>
       <c r="R29" t="n">
-        <v>6325917.340883401</v>
+        <v>6325913</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4155,19 +3759,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4195,15 +3789,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>72810494</v>
+        <v>72810599</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4230,7 +3819,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4247,13 +3836,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522713.9113020768</v>
+        <v>522732</v>
       </c>
       <c r="R30" t="n">
-        <v>6325867.349941096</v>
+        <v>6325914</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4280,19 +3869,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4320,15 +3899,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>72810543</v>
+        <v>72810609</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4355,7 +3929,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4372,10 +3946,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>522731.7456017106</v>
+        <v>522711</v>
       </c>
       <c r="R31" t="n">
-        <v>6325892.450150223</v>
+        <v>6325917</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4405,19 +3979,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4445,15 +4009,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>72810643</v>
+        <v>72810628</v>
       </c>
       <c r="B32" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4480,7 +4039,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4497,10 +4056,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522734.2595391725</v>
+        <v>522744</v>
       </c>
       <c r="R32" t="n">
-        <v>6325930.510618235</v>
+        <v>6325925</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4530,19 +4089,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4570,15 +4119,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>72810470</v>
+        <v>72810643</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4605,7 +4149,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4622,10 +4166,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522687.7647729856</v>
+        <v>522734</v>
       </c>
       <c r="R33" t="n">
-        <v>6325868.293564737</v>
+        <v>6325931</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4655,19 +4199,9 @@
           <t>2018-08-22</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2018-08-22</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4692,6 +4226,336 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>72810665</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bredhälla, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>522710</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6325928</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2018-08-22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2018-08-22</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>72810681</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bredhälla, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>522703</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6325934</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2018-08-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2018-08-22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>72810690</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bredhälla, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>522720</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6325945</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nottebäck</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2018-08-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2018-08-22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>per taube</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
